--- a/plantilla-hojas.xlsx
+++ b/plantilla-hojas.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet name="Ficha" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Informes" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Listas" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Anuladas" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Listas" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -676,6 +677,42 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Motivo</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/plantilla-hojas.xlsx
+++ b/plantilla-hojas.xlsx
@@ -571,7 +571,7 @@
       <formula1>Listas!$A$2:$A$11</formula1>
     </dataValidation>
     <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor no admitido" error="Elige uno de los valores de la lista (hoja «Listas»)." type="list">
-      <formula1>Listas!$B$2:$B$41</formula1>
+      <formula1>Listas!$B$2:$B$42</formula1>
     </dataValidation>
     <dataValidation sqref="R2:R1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor no admitido" error="Elige uno de los valores de la lista (hoja «Listas»)." type="list">
       <formula1>Listas!$C$2:$C$5</formula1>
@@ -713,7 +713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1105,26 +1105,33 @@
     <row r="38">
       <c r="B38" t="inlineStr">
         <is>
-          <t>Baile flamenco</t>
+          <t>Danza</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="inlineStr">
         <is>
-          <t>Danza clásica</t>
+          <t>Baile flamenco</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" t="inlineStr">
         <is>
-          <t>Danza contemporánea</t>
+          <t>Danza clásica</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" t="inlineStr">
+        <is>
+          <t>Danza contemporánea</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Danza española</t>
         </is>

--- a/plantilla-hojas.xlsx
+++ b/plantilla-hojas.xlsx
@@ -599,7 +599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -610,8 +610,9 @@
     <col width="26" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
     <col width="31" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -657,12 +658,17 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Necesidades específicas de apoyo educativo</t>
+          <t>Necesidades de apoyo</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Justificación y orientaciones</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Centro Docente</t>
         </is>
       </c>
     </row>
